--- a/AAII_Financials/Quarterly/RELX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RELX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>RELX</t>
   </si>
@@ -656,24 +656,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -684,352 +684,378 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3231400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3216000</v>
+      </c>
+      <c r="F8" s="3">
         <v>3263100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3259000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3247700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3062700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3000200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3212000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2932600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2930700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2969100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2844600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2858600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2782900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2761600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4618100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4343300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4945800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4554000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4683200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4862500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5146800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4931500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>4473200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4210700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3922100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3903000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3852900</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1082000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1076800</v>
+      </c>
+      <c r="F9" s="3">
         <v>1098900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1097500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1096000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1033600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1058500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1133200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1016700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1016100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1030500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>987200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1015400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>988500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>988600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1579000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1554500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1723500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1600000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1640800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1729100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1802900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1802700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1617100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1519100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1445200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1344400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1355000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2149400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2139200</v>
+      </c>
+      <c r="F10" s="3">
         <v>2164200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2161500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2151700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2029100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1941700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2078800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1915900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1914700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1938700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1857300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1843300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1794500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1773000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3039100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2788900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3222400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2954000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>3042400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3133400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3343900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3128800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2856100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2691600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2476900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2558500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2498000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,55 +1085,57 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>127400</v>
+      </c>
+      <c r="F12" s="3">
         <v>120500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>120300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>118500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>111800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>117100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>125300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>111800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>111800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>107600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>103100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>102300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>99600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>186200</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>8</v>
@@ -1142,8 +1170,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,139 +1259,151 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="F14" s="3">
         <v>-4000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-4000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-1900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>2500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>2700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>23600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>22600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>22200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>21600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>158700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-7400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>7400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-66800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>43900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-4000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>11300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-30600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>44300</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-50900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>65800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>85800</v>
+      </c>
+      <c r="F15" s="3">
         <v>53800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>53800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>93800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>88500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>50700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>54300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>94200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>94100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>61100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>58600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>103600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>100800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>74100</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1391,8 +1437,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,174 +1471,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2197200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2186700</v>
+      </c>
+      <c r="F17" s="3">
         <v>2238200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2235400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2245500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2117600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2116400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2265800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2044800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2043500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2106800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2018400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2044700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1990500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2026000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3463900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3409200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3646700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3259700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3513300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3568700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3795300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3646700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3427500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3146700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2879900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2998300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2919300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1034200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1029300</v>
+      </c>
+      <c r="F18" s="3">
         <v>1024900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1023600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1002200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>945100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>883900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>946300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>887800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>887200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>862300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>826200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>813900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>792400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>735600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1154200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>934200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1299100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1294300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1169900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1293800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1351400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1284800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1045600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1064000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1042100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>904600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>933600</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,222 +1682,236 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F20" s="3">
         <v>7400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>7400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-18500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-17400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-16400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-16400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-17200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-16700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-108800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-107900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-250600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-120600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-135400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-133100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-135900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-137100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-151500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-116400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-114800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-113200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-113200</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1137700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1132300</v>
+      </c>
+      <c r="F21" s="3">
         <v>1071300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1070000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1114500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1051000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>931400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>997200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>998400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>997800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>921600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>882900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>934700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>909900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>808500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1653300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1282800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1482800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1563700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1451700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1572000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1641500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1620300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1379400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1300600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1273000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1127200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1169300</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>72000</v>
+      </c>
+      <c r="F22" s="3">
         <v>36300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>36300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>150000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>141500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>89500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>95800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>87200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>87100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>100600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>96400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>90200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>87800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>60800</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1865,174 +1945,192 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1010300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1005500</v>
+      </c>
+      <c r="F23" s="3">
         <v>987200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>986000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>878900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>828800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>790000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>845700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>818300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>817800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>737500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>706600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>722400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>703300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>671700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1045400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>826200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1048500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1173600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1034500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1160700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1215600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1147700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>894100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>947600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>927400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>791400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>230900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>229800</v>
+      </c>
+      <c r="F24" s="3">
         <v>247600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>247300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>208200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>196400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>190300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>203700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>195300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>195100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>154800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>148300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>167700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>163300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>146400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>193200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>153800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>142700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>261200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>131700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>255600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>329700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>237000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>157600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>223700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>212600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>177800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,174 +2212,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>779500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>775800</v>
+      </c>
+      <c r="F26" s="3">
         <v>739600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>738600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>670600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>632400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>599700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>642000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>623000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>622600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>582700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>558300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>554700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>540000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>525300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>852200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>672400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>905800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>912400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>902700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>905100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>885900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>910700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>736500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>724000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>714800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>613600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>663700</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>778200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>774500</v>
+      </c>
+      <c r="F27" s="3">
         <v>732800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>731900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>668600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>630500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>594000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>636000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>622400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>622000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>577600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>553400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>555300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>540600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>525900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>865000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>679800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>900800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>912400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>897800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>902500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>877400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>908000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>729100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>721400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>709500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>611000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2407,11 +2529,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2419,20 +2541,20 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>9800</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W29" s="3">
-        <v>489600</v>
+        <v>9800</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>489600</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2440,14 +2562,20 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,174 +2746,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-7400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-7400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>18500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>17400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>16400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>16400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>17200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>16700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>108800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>107900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>250600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>120600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>135400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>133100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>135900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>137100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>151500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>116400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>114800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>113200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>113200</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>778200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>774500</v>
+      </c>
+      <c r="F33" s="3">
         <v>732800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>731900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>668600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>630500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>594000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>636000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>622400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>622000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>577600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>553400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>555300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>540600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>525900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>865000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>679800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>900800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>912400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>907600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>902500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1367000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>908000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>729100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>721400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>709500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>611000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,179 +3013,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>778200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>774500</v>
+      </c>
+      <c r="F35" s="3">
         <v>732800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>731900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>668600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>630500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>594000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>636000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>622400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>622000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>577600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>553400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>555300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>540600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>525900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>865000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>679800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>900800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>912400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>907600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>902500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1367000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>908000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>729100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>721400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>709500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>611000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,91 +3266,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>291900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>290500</v>
+      </c>
+      <c r="F41" s="3">
         <v>176300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>176100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>289100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>272600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>149000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>159500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>176900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>176800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>197400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>189100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>125800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>122500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>402400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>112600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>241900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>171200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>138200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>139100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>139800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>157100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>213000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>199500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>272800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>159100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>189600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>363400</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3260,589 +3440,637 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3106000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3091200</v>
+      </c>
+      <c r="F43" s="3">
         <v>2927300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2923600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2955200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2786900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2789300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2986200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2724700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2723000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2592100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2483300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2531400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2464400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2524200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2465800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2235600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2564700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2063800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2458100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2140400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>2650500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2168900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2481700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1910800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2088200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1677600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1958100</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>432500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>430500</v>
+      </c>
+      <c r="F44" s="3">
         <v>418600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>418000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>420600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>396600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>414400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>443600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>412000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>411700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>405100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>388100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>395200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>384700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>372300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>307100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>294000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>269300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>250700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>258600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>264900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>278800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>268900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>257400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>243000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>206100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>193600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>187000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F45" s="3">
         <v>67300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>67200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>80800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>76200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>43800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>46900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>48000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>48000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>99400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>95200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>108000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>105200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>25300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>24300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>16100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>28500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>19900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>12200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>29300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>41000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>22600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>24600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>16800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>40400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>52700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3867600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3849200</v>
+      </c>
+      <c r="F46" s="3">
         <v>3983800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3978800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3745700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3532300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3750800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4015500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3361700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3359500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3660800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3507200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3160500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3076800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3697800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2909800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2787600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3033800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2472600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2868000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2574300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3127400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2673500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2963200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>2443400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2493800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>2113400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2549300</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>455100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>452900</v>
+      </c>
+      <c r="F47" s="3">
         <v>397000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>396500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>397300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>374700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>326800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>349800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>360200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>359900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>350300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>335600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>367300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>357500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>344600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>497800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>373400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>349900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>384200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>311100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>326100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>343900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>312900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>294400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>334800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>315600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>256800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>312100</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>238800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>237700</v>
+      </c>
+      <c r="F48" s="3">
         <v>214000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>213700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>212400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>200300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>214100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>229200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>247700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>247500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>270000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>258700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>301200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>293200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>326500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>483700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>535900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>550900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>538800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>562400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>624300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>680700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>676400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>676100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>298600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>298700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>280500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>298900</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14877300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>14806500</v>
+      </c>
+      <c r="F49" s="3">
         <v>14807500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>14788800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>14830800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>13986000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>14246900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>15252600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>14255600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>14246400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>14343800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>13742000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>14418400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>14036500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>14352700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>13626600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>14332700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>12750500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>12443900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>12727200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>13285700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>12961000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>12571100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>12311100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>11882200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>10939200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>10435600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>10725300</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>404100</v>
+      </c>
+      <c r="F52" s="3">
         <v>358000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>357600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>324700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>306200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>301700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>323000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>269200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>269000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>212700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>203800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>233800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>227600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>174700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>582200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>534700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>424400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>661800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>608700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>668200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>762700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>705600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>645400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>650300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>541300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>680800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>713700</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19944300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>19849300</v>
+      </c>
+      <c r="F54" s="3">
         <v>19861400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>19836300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>19626000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>18508000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>18945400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20282800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>18595400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18583400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>19000600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>18203500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>18631100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>18137600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>19072200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>18100100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>18564300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>17109400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>16501300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>17077400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>17478700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>17875700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>16939400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>16890200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>15609400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>14588700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>13767000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>14599300</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5315100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5289800</v>
+      </c>
+      <c r="F57" s="3">
         <v>119800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>119600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5056900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4768800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>279200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>298900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4553400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4550500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>217800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>208700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4369000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4253300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>155400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4171500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3976100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>4316700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3639200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4186700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3884100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4667000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3954300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>4284700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3529400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3783800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2983800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3471100</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3108700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3093900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2114400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2111700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2660600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2509100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1767700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1892500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2247000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2245600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1672400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1602300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1949400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1897800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1048300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1083800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1509800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2556000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1296600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1698100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1622600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1078300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1030500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1439700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1129900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>813900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>539900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>890200</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>196400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>195400</v>
+      </c>
+      <c r="F59" s="3">
         <v>4263800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4258400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>193200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>182200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3819600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4089300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>247700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>247500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3808500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3648700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>332900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>324100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3837600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>341700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>420600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>506200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>578600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>606300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>797300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>854700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>853400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>879400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>897200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>849100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>754500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8620100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8579100</v>
+      </c>
+      <c r="F60" s="3">
         <v>8076700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8066500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7910700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7460000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7158500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7663900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7048200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7043600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6992900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6699500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6651300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6475200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6249800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5597000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>5906500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>7379000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5514500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>6491100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>6304100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>6600100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>5838200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>6603800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>5556500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>5446800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>4278300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>5182900</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8707700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8666300</v>
+      </c>
+      <c r="F61" s="3">
         <v>7666200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7656500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7662700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7226200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6424900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6878400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6549000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6544700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6603100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6326100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6689500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6512300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>7060700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8030800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>8201600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>5402400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>6756100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>6066600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>6868500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>6355300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>6414700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>5033500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>5098800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>4275500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>4669300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>4146600</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>148600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>147900</v>
+      </c>
+      <c r="F62" s="3">
         <v>149400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>149200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>208200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>196400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>176500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>189000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>184500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>184400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>189800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>181800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>260500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>253600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>306000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1783800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1854700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1610600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1616400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1642000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1426900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1647200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2214100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2410200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2356800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2025600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2416300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2455800</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18279200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18192100</v>
+      </c>
+      <c r="F66" s="3">
         <v>16644700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>16623700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>16620100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>15673300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14558600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>15586400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14572800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14563400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14620200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14006800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>14503600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>14119400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>14549100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>15414200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>15985100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>14421800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>13918600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>14236200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>14623500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>14632200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>14512300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>14094400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>13060000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>11792300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>11406000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>11826100</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,8 +5853,14 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5555,47 +5903,53 @@
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S72" s="3">
         <v>1553400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>972600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1214700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1344700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1200400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>824000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>601400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>33300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-264800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>262400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>444800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>184400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>140900</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1642600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1634700</v>
+      </c>
+      <c r="F76" s="3">
         <v>3184400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3180400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2986700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2816600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4358000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4665600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4059300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4056700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4407200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4222300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4158000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4047900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4549700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2685900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2579200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2687600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2582700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2841100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2855200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3243400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2427100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2795700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2549400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2796400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>2361000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>2773200</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,179 +6387,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>778200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>774500</v>
+      </c>
+      <c r="F81" s="3">
         <v>732800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>731900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>668600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>630500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>594000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>636000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>622400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>622000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>577600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>553400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>555300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>540600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>525900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>865000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>679800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>900800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>912400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>907600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>902500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1367000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>908000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>729100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>721400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>709500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>611000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,91 +6607,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F83" s="3">
         <v>25700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>27500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>27200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>27200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>35700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>34200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>33000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>32200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>34300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>31800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>32200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>34800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>48700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>372400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>289100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>270500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>253000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>265900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>276900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>284400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>335500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>357200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>243000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>238700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>237000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>967900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>963300</v>
+      </c>
+      <c r="F89" s="3">
         <v>956900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>955700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>968600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>913400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>844400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>904000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>795600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>795000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>814600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>780400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>748500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>728700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>776600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1039000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>972600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1374800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1149000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1319900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1202000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1430700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1202300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1264900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>923100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1021300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>821700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>923100</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-6100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-6000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-8200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-7800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-8000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-5100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-10800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-10400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-8300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-8000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-194000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-168000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-209000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-24600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-42700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-28000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-45300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-25300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-45600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-53500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-376600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-193600</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-245500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-244300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-177700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-177400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-346600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-326900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-210900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-225800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-150400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-150300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-153500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-147000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-208400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-202900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-193400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-385200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1081800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-420600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-461500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-551400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1090200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-349500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-223700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-594900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-228800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-250400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-302900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-509600</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,91 +7652,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>564500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>561900</v>
+      </c>
+      <c r="F96" s="3">
         <v>240200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>239900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>564500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>532300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>212200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>227200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>494100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>493800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>204400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>195900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>468900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>456500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>181300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-336500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-765500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-327600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-677000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-302500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-729400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-338200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-696300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-269700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-599900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-211300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-554400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-206700</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-664100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-660900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-834500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-833400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-555600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-523900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-647900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-693600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-650900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-650400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-623500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-597300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-685000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-666800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-447600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-784400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>172400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-923200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-685200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-758800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-121100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1092500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-930600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-639200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-628300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-795600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-676800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-3800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-3800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-4400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-4300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>4200</v>
-      </c>
-      <c r="M101" s="3">
-        <v>3900</v>
-      </c>
-      <c r="N101" s="3">
-        <v>3600</v>
       </c>
       <c r="O101" s="3">
         <v>3900</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Q101" s="3">
+        <v>3900</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-6400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>7400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-6200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>2300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>49100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-15800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>58800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-53800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-53800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>63000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>59400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-13100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-14100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-9500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-9500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>35700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>34200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-149300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-145400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>139800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-136900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>70700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>24800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>4700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>11000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-8000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-69300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-60300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>115100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-28700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-173800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>159300</v>
       </c>
     </row>
